--- a/output/Ningxia/石嘴山市_news.xlsx
+++ b/output/Ningxia/石嘴山市_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,22 +518,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>项目初步设计审批</t>
+          <t>审核结果公布</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>自治区发改委统筹管理，宁夏回族自治区投资项目在线审批监管平台</t>
+          <t>企业信息资质审核结果公示、产品信息资质审核结果公示、申（投）诉时间及方式</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -570,17 +570,15 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/46195a0a3b9844d69248075574a0a7ba</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/06883182b278466ab0f19bc81acf4908</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -592,22 +590,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>社会团体住所变更</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）住所信息</t>
+          <t>集中采购文件及采购目录、采购实施范围、采购药品范围、采购组织机构及工作机构、采购信息发布平台、采购流程、投标人基本要求、采购方式及周期等</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -617,7 +615,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -626,7 +624,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -635,7 +633,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -644,17 +642,15 @@
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/56aa89c2d07c4982a9fc2ed7cabb2da1</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/912022c15af549de831838c0798d011a</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -666,41 +662,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>人力资源服务许可审批</t>
+          <t>耗材招标（挂网采购）项目中标信息</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>该数据由自治区人社厅统筹管理（宁夏行政审批与公共服务系统）人力资源服务许可信息</t>
+          <t>耗材招标（挂网采购）项目中标信息</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -709,7 +705,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -718,17 +714,15 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/5d79e1866af44993b7ea7f0592d693b0</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/be5b2b8a581b446b9708a8ad4f531e4e</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -740,22 +734,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>历年医疗卫生机构门诊服务情况</t>
+          <t>药品采购政策信息</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>年份,总诊疗人次,门急诊人次,互联网诊疗服务人次数,家庭卫生服务人次数,观察室留观病例数,健康检查人数,总诊疗人次中,预约诊疗人次占总诊疗人次百分比()该系统数据由自治区卫健委统筹管理</t>
+          <t>药品采购相关政策信息</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>石嘴山市卫生健康委员会</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -765,7 +759,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -774,7 +768,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -783,7 +777,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -792,17 +786,15 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/653b5078f0714461b6f307b657502c66</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/c39846992b244ca09c174f1d432289cd</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -814,22 +806,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>社会团体修改章程核准</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）章程修改信息</t>
+          <t>生产企业申报条件、申报范围、申报流程、申报时间及地点、申报注意事项及相关资料下载</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -839,7 +831,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -848,7 +840,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -857,7 +849,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -866,17 +858,15 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/6a2f052a1881407a942721260af850c0</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/209e00b6ded74ad28a29c624040d46cc</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -888,22 +878,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>经营性人力资源服务机构开展人力资源服务业务的备案</t>
+          <t>资质审核公布</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>该数据由自治区人社厅统筹管理（宁夏行政审批与公共服务系统）经营性人力资源服务机构开展人力资源服务业务的备案信息</t>
+          <t>资质材料审核信息</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,7 +903,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -922,7 +912,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -931,7 +921,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -940,17 +930,15 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/6d7c2739ed054c66ad5443c7396109da</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/2127b4d600dd4075b265d58a6b2e4fbe</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -962,22 +950,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>劳务派遣经营许可</t>
+          <t>医用耗材采购政策</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>该数据由自治区人社厅统筹管理（宁夏行政审批与公共服务系统）劳务派遣经营公司信息</t>
+          <t>医用耗材采购相关政策</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -987,7 +975,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -996,7 +984,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1005,7 +993,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1014,17 +1002,15 @@
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/70dfa2c1fe7b4eefa571967690015c86</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/466ad1c685d54633b46f7d17d1e789f7</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -1036,41 +1022,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>特种设备作业人员资格认定</t>
+          <t>疫苗招标中标公告</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>该数据由自治区市场监管厅统筹管理（特种设备作业人员考核管理平台（宁夏））</t>
+          <t>疫苗招标中标公告</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1079,7 +1065,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1088,17 +1074,15 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/982968e4db4541629f85e5db466baca3</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/b815f1006a5a495087206d0806d2a7ca</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -1110,41 +1094,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>建设项目用地预审与选址意见书核发</t>
+          <t>药品、疫苗、耗材、检验试剂、中药饮片招标（挂网采购）公告</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>自治区发改委和自治区住建厅统筹管理，宁夏回族自治区投资项目在线审批监管平台和宁夏工程建设项目审批管理平台</t>
+          <t>药品、疫苗、耗材、检验试剂、中药饮片招标（挂网采购）公告</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1153,7 +1137,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1162,12 +1146,10 @@
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/a2b2745951b54a9db2162f69a62789b8</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f8334763b0b848eeb559f19fbf16917d</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1184,22 +1166,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>食品生产经营登记证（小餐饮、小销售店）</t>
+          <t>中标结果公示</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>该数据由自治区市场监管厅统筹管理(宁夏食品经营许可管理系统)</t>
+          <t>公示内容、公示时间、申（投）诉时间及方式、申（投）诉处理结果、注意事项及联系方式</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1209,7 +1191,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1218,7 +1200,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1227,7 +1209,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1236,17 +1218,15 @@
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/ae9531650217426f8fb1540125e0104f</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/428986cad66c4bc99359bcf0c3093321</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -1258,41 +1238,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>社会团体注销登记</t>
+          <t>药品招标（挂网）采购中标公告</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）社会团体注销信息</t>
+          <t>药品招标（挂网）采购中标公告</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1301,7 +1281,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1310,17 +1290,15 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/f6bdbf43698d41c7adc49e9322029d6a</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/a09b489c35064f5981d0299b21af05bb</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -1332,22 +1310,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>对外贸易经营者信息</t>
+          <t>中标目录</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2021年对外贸易经营者信息</t>
+          <t>药品采购中标目录</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>石嘴山市商务局</t>
+          <t>自治区公共资源交易管理局</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1357,16 +1335,16 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>有条件开放</t>
+          <t>无条件开放</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1375,7 +1353,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1384,17 +1362,15 @@
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/22de9ce2f98744da9306afd33023f2c6</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/d19f2cb1ba304539ae572eef2bdce43d</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1382,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>历年医疗机构床位数</t>
+          <t>宁夏高速公路气象预报</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1416,22 +1392,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>机构分类,编制床位数,实有床位数,实有床位增长数,实有床位增长率该系统数据由自治区卫健委统筹管理</t>
+          <t>宁夏高速公路气象预报</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>石嘴山市卫生健康委员会</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1444,31 +1420,29 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>['接口']</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/2ed7275a5faf4d8a8e7c000583db3d7c</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/4ec7dcf84ad14166a951a8a8463f2c9e</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1454,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>从事拍卖业务许可</t>
+          <t>形势预报</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1490,22 +1464,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>拍卖企业信息</t>
+          <t>形势预报</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>石嘴山市商务局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1514,7 +1488,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>125409</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1523,26 +1497,24 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/3a4913ee23204f48b7a76dcc955b42c6</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/98e60cd067ac4e09a3fb5abc37b2a913</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>实时</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1526,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>经营性人力资源服务机构设立分支机构的书面报告</t>
+          <t>地质灾害气象风险预警</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1564,22 +1536,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>该数据由自治区人社厅统筹管理（宁夏行政审批与公共服务系统）经营性人力资源服务机构设立分支机构的备案信息</t>
+          <t>地质灾害气象风险预警</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1588,7 +1560,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>125409</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1597,26 +1569,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/441f87b364bb4851bc54f1922e901449</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/b1ca3b0cfa124d7abef83c6d83b5fa9b</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1598,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>特种设备档案（压力容器、电梯、起重机械、场内车辆、大型游乐设施、锅炉）</t>
+          <t>山洪灾害气象风险预警</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1638,22 +1608,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>改数据由自治区市场监管厅统筹管理（特种设备安全监管系统）</t>
+          <t>山洪灾害气象风险预警</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1662,7 +1632,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>125409</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1671,26 +1641,24 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/0c89fcaeee0f43ba906c5f98108d7e35</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/ccca54d056994223947713de0222f264</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1670,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>社会团体法人登记证书到期换证</t>
+          <t>森林火险气象等级预报</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1712,22 +1680,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）社会团体登记证书信息</t>
+          <t>森林火险气象等级预报</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1736,7 +1704,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>125409</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1745,26 +1713,24 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/1b1ed6e09a4440e9ba6a3ba8887909f2</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/d7f39c06fb7b4e04ac7a422e98984f24</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1742,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>施工图设计审查</t>
+          <t>基于位置查询天气实况数据</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1786,22 +1752,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>由自治区发改委统筹管理（宁夏回族自治区投资项目在线审批监管平台）</t>
+          <t>基于位置查询天气实况数据</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1814,31 +1780,29 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>['接口']</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/235ef88e01624ee3b62a4c5cf825fb2a</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/33b431afeb09435f940e24a0e742c417</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1814,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>环境影响报告表审批</t>
+          <t>公众预报</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1860,22 +1824,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>由自治区公厅统筹管理（宁夏行政审批与公共服务系统）</t>
+          <t>公众预报</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1884,35 +1848,33 @@
         </is>
       </c>
       <c r="I20" t="n">
+        <v>125409</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>['xls']</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/28c9ddb0b33f43bbb3df53e0868a316f</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/420c25e3df454e7bbf8fc6686f80babd</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>实时</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1886,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>建筑施工许可</t>
+          <t>基于位置查询天气预报</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1934,22 +1896,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>由自治区住建厅统筹管理（宁夏回族自治区工程建设项目审批管理系统）</t>
+          <t>基于位置查询天气预报</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1962,31 +1924,29 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>['接口']</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/404b81f69e454f03a77d0d00e8f2b917</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/4c0441717a594ec0a7f85a0839363005</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1958,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>气瓶充装许可</t>
+          <t>宁夏主要景区预报</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2008,22 +1968,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>无专业系统，数据自行管理</t>
+          <t>宁夏主要景区预报</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2036,31 +1996,29 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>['接口']</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/56711b381fea4285bd452816dfea3669</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/5dfb7522317240a4b9b9b0758c1acdfd</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>实时</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>车用气瓶使用登记</t>
+          <t>暴雨、大风、雷电等灾害性天气预警信号</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2082,22 +2040,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>该数据由自治区市场监管厅统筹管理（CNG电子标签管理系统）</t>
+          <t>暴雨、大风、雷电等灾害性天气预警信号</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2106,7 +2064,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>125409</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2115,26 +2073,24 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/5c23a5728d5744b183e15b237f771f2d</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/6e2050c916de4eca85fe365dbfd97fbb</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -2146,32 +2102,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>商品房预售许可</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
+          <t>城市生活气象指数预报</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>由自治区办公厅统筹管理（宁夏行政审批与公共服务系统）</t>
+          <t>城市生活气象指数预报</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2180,7 +2132,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>125409</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2189,26 +2141,24 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/68c89025a24a4a5991b0046ddf164baa</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/c670d1c98bc047d0a75c44204115f3ae</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2170,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>单用途商业预付卡企业信息</t>
+          <t>臭氧污染气象条件预报</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2230,22 +2180,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>单用途商业预付卡</t>
+          <t>臭氧污染气象条件预报</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>石嘴山市商务局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2254,7 +2204,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>125409</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2263,26 +2213,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/756896dc376f4e4081662607714977f9</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f501c1c0c4474b2284643f3c208f30bd</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2242,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>项目可行性研究报告审批</t>
+          <t>空气污染扩散气象条件预报</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2304,22 +2252,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>自治区发改委统筹管理，宁夏回族自治区投资项目在线审批监管平台</t>
+          <t>空气污染扩散气象条件预报</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2328,7 +2276,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>125409</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2337,7 +2285,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -2346,17 +2294,15 @@
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/894f6f48fba64565a60e59ac048bf2f6</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/07b07814617e4398be89068254d57793</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -2368,41 +2314,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>气瓶充装许可注销</t>
+          <t>气候评价</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>气象服务</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>无专业系统，数据自行管理</t>
+          <t>气候评价</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区气象局</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2411,7 +2357,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -2420,17 +2366,15 @@
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/9166a30ccfb34433b40160bb04b29d24</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/bd14ad3e741c40f182f0301115d7449a</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -2442,41 +2386,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>成品油品零售经营信息</t>
+          <t>排污机动车信息</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>成品油零售</t>
+          <t>排污机动车信息</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>石嘴山市商务局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2485,7 +2429,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -2494,12 +2438,10 @@
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/978895140d964311a2f7f6bd85324b7d</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/6d3831f992ca40e3a616d8ff234a5b1a</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2516,41 +2458,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>历年医疗卫生机构住院服务情况</t>
+          <t>企业排污许可信息</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>年医疗卫生机构住院服务情况该系统数据由自治区卫健委统筹管理</t>
+          <t>企业排污许可信息</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>石嘴山市卫生健康委员会</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2559,7 +2501,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -2568,17 +2510,15 @@
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/9a31f35c82ea40e88fba29ece3c6251e</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/daaaaceb04464113b9ca836e48ef16c9</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -2590,41 +2530,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>二手车市场信息</t>
+          <t>企业排污费征收信息（月）</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>二手车市场</t>
+          <t>企业排污费征收信息（月）</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>石嘴山市商务局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2633,7 +2573,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -2642,17 +2582,15 @@
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/aa338ee955e44d5892d1107c17eaecdb</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/e925bd6c50c74ca4b4ee2c68e44b5fa2</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>每半年</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -2664,41 +2602,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>食品经营许可</t>
+          <t>污染源废气在线监测日信息</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>该数据由自治区市场监管厅统筹管理(宁夏食品经营许可管理系统)</t>
+          <t>污染源废气在线监测日信息</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2707,7 +2645,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -2716,17 +2654,15 @@
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/aef9f617c6a843868565b36af8ef9e10</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/98040a637f164dcf9b1716a359571148</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -2738,41 +2674,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>民办非企业单位法人登记证书到期换证</t>
+          <t>政务公文（收文）</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）民办非企业单位登记证书信息</t>
+          <t>政务公文（收文）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2781,7 +2717,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -2790,17 +2726,15 @@
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/b69b9ad70480453d8daa68ba1ab8749a</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/c0550e76be054734a32e1d6f6e9b4ef3</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -2812,41 +2746,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>燃气经营许可</t>
+          <t>银川市环境监察执法公开企业列表</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>由自治区办公厅统筹管理（宁夏行政审批与公共服务系统）</t>
+          <t>银川市环境监察执法公开企业列表</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2855,7 +2789,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -2864,17 +2798,15 @@
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/d3ff88946c6c416cb6e4978e0aa0a90c</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/cfa2df95f5c3491e9a33309341fe940f</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -2886,41 +2818,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>历年病床使用情况</t>
+          <t>环境监察执法（污染源现场监察记录信息）</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>历年病床使用情况,该系统数据由自治区卫健委统筹管理</t>
+          <t>环境监察执法（污染源现场监察记录信息）</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>石嘴山市卫生健康委员会</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2929,7 +2861,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -2938,12 +2870,10 @@
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/de5217e086a24a5c9bc05f59536eceb6</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/d281cd6f2f27448f843194185fff6482</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2960,41 +2890,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>特种设备档案（气瓶）</t>
+          <t>机动车检测机构信息</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>改数据由自治区市场监管厅统筹管理（特种设备安全监管系统）</t>
+          <t>机动车检测机构信息</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3003,7 +2933,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -3012,17 +2942,15 @@
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/e2b894f0117b43218be36c13de2289d8</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/74a5c5cf736747b380e7623795d4b946</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -3034,41 +2962,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>企业实行不定时工作制和综合计算工时制等其他工作和休息办法审批</t>
+          <t>建设项目环境影响评价审批信息</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>该数据由自治区人社厅统筹管理（宁夏行政审批与公共服务系统）申请企业实行不定时工作制和综合计算工时制的公司信息</t>
+          <t>建设项目环境影响评价审批信息</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3077,7 +3005,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -3086,17 +3014,15 @@
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/e8f6ededa4724ff98cc716ddfd836898</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/b9c813f73230473c916d472cb05ae294</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -3108,41 +3034,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>生产建设项目水土保持方案审批</t>
+          <t>政务公文（发文）</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>自治区发改委统筹管理，宁夏回族自治区投资项目在线审批监管平台</t>
+          <t>政务公文（发文）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3151,7 +3077,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -3160,17 +3086,15 @@
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/f226f27311944047a46da395bcfa7346</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/04dae815f97a494abdb4ed77c9b0795a</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>实时</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -3182,41 +3106,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>企业登记信息</t>
+          <t>城市空气质量监测信息</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>企业登记基本信息</t>
+          <t>城市空气质量监测信息</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3225,7 +3149,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -3234,17 +3158,15 @@
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/f5103d03ceb94a4e9005b48b1de17d24</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/176e830451cb4b178d67690dee01eac8</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -3256,41 +3178,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>建设工程（含临时建设）规划类许可证核发</t>
+          <t>重点排污单位名单</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>自治区发改委和自治区住建厅统筹管理，宁夏回族自治区投资项目在线审批监管平台和宁夏工程建设项目审批管理平台</t>
+          <t>重点排污单位名单</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3299,7 +3221,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -3308,12 +3230,10 @@
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/1dbeee00fecd43a9b54c2b92e97a18c5</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/3be3e237ec314cf4ab608b626d730dd6</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3330,41 +3250,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>特种设备停用（重新启用）、报废、注销登记</t>
+          <t>行政处罚信息</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>改数据由自治区市场监管厅统筹管理（特种设备安全监管系统）</t>
+          <t>行政处罚信息</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3373,7 +3293,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -3382,17 +3302,15 @@
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/206d8484e9f541dbbfa01006ba704a13</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/5689b5d0462941b4845863841123c480</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -3404,41 +3322,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>企业投资项目核准</t>
+          <t>银川市自行监测信息公开企业列表</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>自治区发改委统筹管理，宁夏回族自治区投资项目在线审批监管平台</t>
+          <t>银川市自行监测信息公开企业列表</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3447,7 +3365,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -3456,17 +3374,15 @@
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/246bd531bbe74f5296e0c4f055e01d31</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/5f3023b28d1c4ef0828f09d90eb55470</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -3478,41 +3394,41 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>第二类医疗器械经营备案</t>
+          <t>监测站空气质量监测信息</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>该数据国家药品监督管理局统筹管理（医疗器械生产经营许可（备案）信息系统）</t>
+          <t>监测站空气质量监测信息</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3521,7 +3437,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -3530,12 +3446,10 @@
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/30b27367b7e34038bf8847c5909f9caa</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/06f070af0130491eaa642a9608063cc8</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3552,41 +3466,41 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>环境影响报告书审批</t>
+          <t>污染源废水在线监测日数据</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>由自治区办公厅统筹管理（宁夏行政审批与公共服务系统）</t>
+          <t>污染源废水在线监测日数据</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3595,7 +3509,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -3604,17 +3518,15 @@
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/336c5e9b9a3d44cdb7fdc0399d5d245c</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/42b3cf272c6b4ec0a60686d14bb0549d</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -3626,41 +3538,41 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>社会团体业务主管单位变更登记</t>
+          <t>空气质量监测站信息</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）业务主管单位变更信息</t>
+          <t>空气质量监测站信息</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区生态环境厅</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3669,7 +3581,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -3678,17 +3590,15 @@
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/38dfad181699458aa977ae8f6fae345a</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/468d78b59ffc43c6a8c314226b299f8c</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3610,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>获评自治区数字化车间</t>
+          <t>健康档案</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3710,27 +3620,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>自治区工信厅认定数字化车间企业</t>
+          <t>健康档案</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>石嘴山市工业和信息化局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3747,22 +3657,20 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/3ba26d4d9cbe43f58965a4b1bf870dce</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/828ca5b2e8ba4429a77dd96dd2faf94f</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>每月</t>
         </is>
       </c>
     </row>
@@ -3774,41 +3682,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>食品生产许可</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
+          <t>出生医学证明信息</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>该数据由自治区市场监管厅统筹管理（宁夏食品生产监督管理信息系统）</t>
+          <t>出生医学证明信息</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3817,26 +3721,24 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/3fd4775d46584a15b223b338ced34af6</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/8e8f79a1ecdc482493678f0cab7efa6e</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>实时</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -3848,32 +3750,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>食品生产经营登记证（小作坊）</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
+          <t>自治区核酸检测定点医院</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>该数据由自治区市场监管厅统筹管理（宁夏食品生产监督管理信息系统）</t>
+          <t>自治区核酸检测定点医院</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3891,7 +3789,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>['其他']</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -3900,12 +3798,10 @@
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/46584b46d7194291ad5091e32feaabd9</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/cd3c8dc0bf3a4e37b42995186c54cbaf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3922,7 +3818,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>民办非企业单位注销登记</t>
+          <t>电子病历信息</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3932,31 +3828,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）民办非企业单位注销信息</t>
+          <t>电子病历信息</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3965,26 +3861,24 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/512584e6be204e8081e56225a56aa137</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/da732dcf583b4b25a5a49a45d9670617</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -3996,32 +3890,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>建设用地规划许可证核发</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
+          <t>最新疫情地图实时数据报告</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>自治区发改委和自治区住建厅统筹管理，宁夏回族自治区投资项目在线审批监管平台和宁夏工程建设项目审批管理平台</t>
+          <t>最新疫情地图实时数据报告</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4030,7 +3920,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -4039,21 +3929,19 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/520217adf76e4d3ba1dda8b5474d69d2</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/de7cb9f95cc74810bf942f0f5821c2f3</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4070,32 +3958,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>事业单位法人登记信息</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
+          <t>2021宁夏公务员考试政策疫情防控通知</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>事业单位基本信息</t>
+          <t>2021宁夏公务员考试政策疫情防控通知</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>石嘴山市委编办</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4113,7 +3997,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>['其他']</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -4122,12 +4006,10 @@
       <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/5bfbe5730112429088ee6041b69c60a2</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/e2015733ed2e4ac185fd45fa0edf3c1e</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4144,32 +4026,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>历年设备情况</t>
+          <t>宁夏最新新冠疫苗接种单位</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>年份,万元以上设备总价值,万元以上设备台数,50万元以下设备台数,50,99万元设备,100万元及以上设备该系统数据由自治区卫健委统筹管理</t>
+          <t>宁夏最新新冠疫苗接种单位</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>石嘴山市卫生健康委员会</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4187,7 +4069,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>['其他']</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -4196,17 +4078,15 @@
       <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/738177d013724db8a61e6b6e16b0310a</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/8fe8eb801bd34e6f8d1cc5714cdc2a22</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -4218,41 +4098,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>特种设备变更登记</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
+          <t>医师信息</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>改数据由自治区市场监管厅统筹管理（特种设备安全监管系统）</t>
+          <t>医师信息</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -4261,26 +4137,24 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/75ee75bacdf4479abfca3756c3f016c5</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/aca1783442424424a9081925a54b01b8</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4166,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>药品零售企业许可</t>
+          <t>全员人口信息</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4302,31 +4176,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>无专业系统，数据自行管理</t>
+          <t>全员人口信息</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -4335,26 +4209,24 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/814c418fb75d4847993f584207c9881e</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/b59c7f8408ee41539bc15e3320f7777c</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>实时</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4238,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>医疗器械网络销售备案</t>
+          <t>120急救</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4376,31 +4248,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>该数据国家药品监督管理局统筹管理（医疗器械生产经营许可（备案）z信息系统）</t>
+          <t>主要包括120急救任务中的电话、受理时间、派车时刻、救治地点、事件类型等相关信息</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -4409,21 +4281,19 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/8d526dd5719d4a55b67e46e359d1210d</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/0c4fade6e759448dbc0a541fc07d9df5</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4440,41 +4310,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>特种设备档案（压力管道）</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
+          <t>计划生育服务证信息</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>改数据由自治区市场监管厅统筹管理</t>
+          <t>计划生育服务证信息</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -4483,26 +4349,24 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/8ecb9e8de9134b5a9331b1d8d9ae8837</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/455c9262a2b3418192dec5299c94645a</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4378,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>第三类医疗器械经营许可</t>
+          <t>护师信息</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4524,31 +4388,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>该数据国家药品监督管理局统筹管理（医疗器械生产经营许可（备案）信息系统）</t>
+          <t>护师信息</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4557,26 +4421,24 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/921935d5fbb14e03a7423ba8f90a7880</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/14933eb9341349f78baf79d2cf221699</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>实时</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4450,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>国民经济核算</t>
+          <t>计划免疫预防接种信息登记</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4598,31 +4460,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>照制度规定、定期发布的全年全区经济社会发展信息为准，发布时间注明年度</t>
+          <t>计划免疫预防接种信息登记</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>石嘴山市统计局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>40386000</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4631,26 +4493,24 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/95f02288f5284daf82ecd94d80ee7380</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/2e533ddef81e4be6813dc6ee0824c4e1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -4662,32 +4522,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>社会团体成立登</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
+          <t>宁夏疫情情况</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）社会团体信息</t>
+          <t>宁夏疫情情况</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区卫健委</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4696,7 +4552,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4705,26 +4561,24 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/a621cfaf76c3453f8a7a2d15933d2491</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/5119018cc7b1456ea3b046864614044f</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>实时</t>
         </is>
       </c>
     </row>
@@ -4736,41 +4590,41 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>洪水影响评价审批</t>
+          <t>第一类非药品类易制毒化学品生产许可证变更申请书_申请单位基本情况表信息</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>安全生产</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>自治区发改委统筹管理，宁夏回族自治区投资项目在线审批监管平台</t>
+          <t>第一类非药品类易制毒化学品生产许可证变更申请书_申请单位基本情况表信息</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区应急管理厅</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4779,7 +4633,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -4788,17 +4642,15 @@
       <c r="M59" t="n">
         <v>0</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/c7d9428d2ac44b53b9e552ebe3c6e0d6</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f46897dc39ab43458e3037b0f98b2284</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>实时</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -4810,41 +4662,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>项目建议书审批</t>
+          <t>非煤矿矿山企业安全生产许可证延期申请书_取证单位_采掘施工企业信息</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>安全生产</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>自治区发改委统筹管理，宁夏回族自治区投资项目在线审批监管平台</t>
+          <t>非煤矿矿山企业安全生产许可证延期申请书_取证单位_采掘施工企业信息</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区应急管理厅</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4853,7 +4705,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -4862,17 +4714,15 @@
       <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/e3624b64490947a88dca4580bb36bd20</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f4c7bb80d7594c15b772ba0b87707ad5</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -4884,41 +4734,41 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>民办非企业单位信息</t>
+          <t>冒用安全生产许可证或者使用伪造的安全生产许可证的处罚</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>安全生产</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）民办非企业单位信息</t>
+          <t>冒用安全生产许可证或者使用伪造的安全生产许可证的处罚</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区应急管理厅</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4927,7 +4777,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -4936,17 +4786,15 @@
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/e3f6ac59b3904496a77749607da88880</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f69c2ec4edfa4f038b92dd67f6f626b8</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -4958,41 +4806,41 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>欠税公告</t>
+          <t>乙级非煤矿检测检验机构增项申请书_仪器设备设施一览表信息</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>安全生产</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>欠税公告</t>
+          <t>乙级非煤矿检测检验机构增项申请书_仪器设备设施一览表信息</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>石嘴山市税务局</t>
+          <t>自治区应急管理厅</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -5001,7 +4849,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -5010,17 +4858,15 @@
       <c r="M62" t="n">
         <v>0</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/ead272c8a367460894bd2b7c85689415</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fa9cb1dca01348d8961816a4f26f7b11</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -5032,41 +4878,41 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>纳税信用A级纳税人名单</t>
+          <t>公告企业名单信息表信息</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>安全生产</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>纳税信用A级纳税人名单</t>
+          <t>公告企业名单信息表信息</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>石嘴山市税务局</t>
+          <t>自治区应急管理厅</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -5075,7 +4921,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -5084,12 +4930,10 @@
       <c r="M63" t="n">
         <v>0</v>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/eb07118001e549348292b060662ec97b</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fd32f1b6ad0e48cf990a8f6269504d62</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5106,41 +4950,41 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>社会团体法定代表人变更</t>
+          <t>第一类非药品类易制毒生产、经营企业安全审查书_申请单位信息</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>安全生产</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>该数据由国家民政部统筹管理（中国社会组织政务管理平台）法定代表人信息</t>
+          <t>第一类非药品类易制毒生产、经营企业安全审查书_申请单位信息</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>石嘴山市审批局</t>
+          <t>自治区应急管理厅</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>无条件开放</t>
+          <t>有条件开放</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -5149,7 +4993,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>['xls']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -5158,17 +5002,1239 @@
       <c r="M64" t="n">
         <v>0</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>https://opendata.nx.gov.cn/portal/catalog/f60b6879efcb4622805693044c6cbf6f</t>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fd58c0827f4448daae1cdbdecceaea72</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>每季度</t>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>非煤矿矿山（安全标准化等级二级及以上企业）企业安全生产许可证延期申请书_取证单位_尾矿库单位信息</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>非煤矿矿山（安全标准化等级二级及以上企业）企业安全生产许可证延期申请书_取证单位_尾矿库单位信息</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fe24d674cf6a4ac1989fb4b663093c62</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>第一类非药品类易制毒化学品（安全标准化等级二级以下企业）生产许可证变更申请书_申请单位基本情况表信息</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>第一类非药品类易制毒化学品（安全标准化等级二级以下企业）生产许可证变更申请书_申请单位基本情况表信息</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/ffbd0e91ff5644ae98ff509966be1a8c</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>第一类非药品类易制毒生产、经营企业安全条件审查意见书（不予通过）信息</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>第一类非药品类易制毒生产、经营企业安全条件审查意见书（不予通过）信息</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f6e0806126ca49bf88e670db0e7e6923</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>非煤矿矿山企业安全生产许可证审查书_承办部门意见信息</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>非煤矿矿山企业安全生产许可证审查书_承办部门意见信息</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f6e0ecccfe2e4d5883621c729fc51375</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>危险化学品建设项目（项目投资50亿元以下）安全审查书_受委托实施审查单位意见信息</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>危险化学品建设项目（项目投资50亿元以下）安全审查书_受委托实施审查单位意见信息</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f6f91c34204841e3adf15a294f58f3b4</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>安全生产规划中期评估报告_重点工程实施情况评估表</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>安全生产规划中期评估报告_重点工程实施情况评估表</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f734612fc56c431ab1c942f4a8e7729a</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>应急案例信息</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>应急案例信息</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f7d2b72dadb64934bf8fdb30ae584de2</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>第一类非药品类易制毒化学品（安全标准化等级二级及以上企业）生产许可证（正本）信息</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>第一类非药品类易制毒化学品（安全标准化等级二级及以上企业）生产许可证（正本）信息</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/f816e03bbaca43dbbbe4acf88ce5243b</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>乙级安全评价机构综合审查记录表信息</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>乙级安全评价机构综合审查记录表信息</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fa404ca0fbcc46fc8e7a5e1df52bdcc6</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>乙级非煤矿检测检验机构增项申请书_授权签字人申请信息</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>乙级非煤矿检测检验机构增项申请书_授权签字人申请信息</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fa6f72a6adc441b081e4bc32c1365ec8</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>危险化学品建设项目安全审查书_审查人员审查意见及签字信息</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>危险化学品建设项目安全审查书_审查人员审查意见及签字信息</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fbc564ba8965448ea5a0c5076302846a</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>查封扣押处理决定书信息</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>查封扣押处理决定书信息</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fbdfca4e70ed4ba091921759fda9bb89</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>危险化学品建设项目（项目投资50亿元以下）安全审查书_专家组组成人员名单信息</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>危险化学品建设项目（项目投资50亿元以下）安全审查书_专家组组成人员名单信息</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fccce9c923d043a5a18047a60b1dff48</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>乙级非煤矿检测检验机构评审人员公正性与保密声明信息</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>乙级非煤矿检测检验机构评审人员公正性与保密声明信息</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/fda14f0005e147e29a09ee38038b34c7</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>非煤矿矿山企业安全生产许可证（油气服务、采掘施工、地质勘探企业）不予颁发通知书信息</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>非煤矿矿山企业安全生产许可证（油气服务、采掘施工、地质勘探企业）不予颁发通知书信息</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2022-01-17</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/feb6c142ebe54914b69f43f79a9effb9</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>第一类非药品类易制毒生产、经营企业安全条件审查申请书_申请文件和材料清单信息</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>第一类非药品类易制毒生产、经营企业安全条件审查申请书_申请文件和材料清单信息</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/ff0ea948df554a3bbaf2c8d889268d05</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>石嘴山市</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>烟花爆竹生产企业（安全标准化等级二级以下企业）安全生产许可证变更申请书_变更内容信息</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>安全生产</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>烟花爆竹生产企业（安全标准化等级二级以下企业）安全生产许可证变更申请书_变信更内容息</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>自治区应急管理厅</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>有条件开放</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>https://opendata.nx.gov.cn/portal/catalog/ffc7fb71009c4dac81fc3815fc95fdc4</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>每年</t>
         </is>
       </c>
     </row>
